--- a/src/attributions/attributions_ig_traj_182.xlsx
+++ b/src/attributions/attributions_ig_traj_182.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,22 +999,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1056763790825679</v>
+        <v>0.09604398131476169</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2661582659571812</v>
+        <v>0.1018703565752829</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01003772731320099</v>
+        <v>-0.06708951254366274</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1023,22 +1023,22 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.01979208801498059</v>
+        <v>0.01959038875913288</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.242987368219968</v>
+        <v>-0.03995416234772978</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004423945506101552</v>
+        <v>-0.01647063863324022</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -1047,133 +1047,133 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1076971022137111</v>
+        <v>0.03991342029219564</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01605192199234246</v>
+        <v>-0.1030808265228934</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.04460431739448262</v>
+        <v>0.0639577482774145</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.07772532331582976</v>
+        <v>-0.01164291594265516</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.00988950490464704</v>
+        <v>0.01336311765950157</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.009194210549037202</v>
+        <v>-0.03620390905948503</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.04384480141443917</v>
+        <v>0.138636328801247</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03442446281322958</v>
+        <v>-0.03378244488111504</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07982703158461509</v>
+        <v>0.2280512897784994</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1648594835943316</v>
+        <v>0.2907186153293516</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09513739437549891</v>
+        <v>-0.02222170054490902</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01400073286441289</v>
+        <v>0.03691980424514012</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02905379851713809</v>
+        <v>-0.08591172598412125</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.09983054286285226</v>
+        <v>0.04641167533977573</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03683329100565719</v>
+        <v>-0.09924491834874911</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,58 +1182,58 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.02957401969734591</v>
+        <v>-0.06726269589256882</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04199075926153524</v>
+        <v>-0.09434118678451599</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.09521321784165342</v>
+        <v>-0.02246730144004375</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.04027809927706854</v>
+        <v>0.1254695188466322</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02140014096010549</v>
+        <v>-0.1367551608127054</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02033857839823998</v>
+        <v>0.0006360008269221169</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1245,73 +1245,73 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03341464267615306</v>
+        <v>-0.1275007827619549</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.04024297188919205</v>
+        <v>-0.04319523098690266</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01772990530384111</v>
+        <v>-0.01742311203747087</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01476736764181623</v>
+        <v>-0.1060346353894533</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.03804480328825097</v>
+        <v>0.1442528763573444</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.04306717921016637</v>
+        <v>-0.01333600769808695</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04779099857713974</v>
+        <v>-0.1276520766543953</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04395842935551074</v>
+        <v>-0.03629189639416435</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.009211424765332644</v>
+        <v>0.006139917814149519</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1323,49 +1323,49 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.03461260656283643</v>
+        <v>-0.08090641994850872</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01670588914064872</v>
+        <v>0.06303409844770626</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0364763747653508</v>
+        <v>-0.0005208451230348522</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.03330360949037436</v>
+        <v>-0.0006447144041238914</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04664660442182604</v>
+        <v>-0.02032925969263832</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.02493578984991634</v>
+        <v>0.01956636975777276</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,52 +1377,52 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.06875348702283682</v>
+        <v>0.02068183392073931</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.01307614595831994</v>
+        <v>0.1342215203434504</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03573607780103341</v>
+        <v>0.2347229060298745</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04906983317781602</v>
+        <v>-0.1079418643360366</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.08964384050486533</v>
+        <v>0.1825700475793036</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.03308765702123937</v>
+        <v>0.03129399630058897</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04350483282345033</v>
+        <v>-0.08208589058238928</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.03706498798249654</v>
+        <v>0.02300595407401788</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.02057055545050679</v>
+        <v>0.00365525305079171</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1452,28 +1452,28 @@
         <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04262581418030015</v>
+        <v>-0.1611431935896082</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.03410540786464537</v>
+        <v>-0.009010681849802502</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01800334742361566</v>
+        <v>-0.0100526199243828</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
@@ -1482,82 +1482,82 @@
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.004411514900748431</v>
+        <v>-0.1538992637991394</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.01531828095525909</v>
+        <v>-0.03018041003936608</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.008546415680021329</v>
+        <v>0.101283731392989</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01248113415308976</v>
+        <v>-0.1493549853351264</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.00559501352612642</v>
+        <v>0.2069368901825876</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.004684377672604515</v>
+        <v>-0.05007433028409148</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.04212936183134562</v>
+        <v>-0.04631138481530252</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02691007616132334</v>
+        <v>-0.006417141885206111</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,37 +1568,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.03881758509682377</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.01144913773058403</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.03882513079484162</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.01580637374640331</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,175 +1607,175 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.002368057020551579</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.008217050300665539</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.03142542710161492</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.02996884246935865</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.02456735840178077</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.00491177457328432</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.02689444263370415</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.03640596047861707</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0.001826225389346287</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.05092282335755816</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.01126758461036499</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.02527633088639523</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.06597060832761693</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.04514618187815272</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.01355634420095259</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.04117349070579794</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0.003791348406290517</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.03599132852790626</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.05827820328677685</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.00104276168331667</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1784,61 +1784,61 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.003556003167204292</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.03101540054624793</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.02103370380585636</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.02743263180066792</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.02625819887297352</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.01780100158864917</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.0002108288923860008</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.05622323501557654</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.01572709204562188</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.02344641784585471</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.036798743139311</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.02646920045896645</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,52 +1892,52 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.004634623442598385</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.04115261080038802</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.00649490470666378</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.01342240672100003</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.03218959899944086</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.01177559353345375</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,37 +1946,37 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0.005910742250407063</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.02755154109442587</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.05288374123947682</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.02472108207114347</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.01775859454382619</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.007538118420614326</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.01638420037985397</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.04387785141786232</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0.005659430923091823</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.03332313229721644</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2039,99 +2039,7496 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.0429005047781064</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.02779495519771542</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.0215251480493142</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.02340781384936826</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.004245051886609586</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.003757879877047303</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.03567142194343965</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.01847273174546256</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.004642820322429781</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.02609724007997925</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4156361622552384</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06402614981271625</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3062711062396781</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2236726671855697</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.02798260886441799</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.05640804838260031</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1239784003852151</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.1191405021153036</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1319236355349414</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1258174301418703</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.04158376180607815</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1111561334226251</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1346889778897059</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.00449809614109023</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.2281554141082583</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.6840768914964721</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.2744150748697978</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.3821610767677349</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.1438038280839145</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.06016669755919993</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1650289695328564</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.04351871273202955</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.1299989630554755</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1453081828967192</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2486519848476308</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.09605381636326868</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.270449917988661</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2843767478193017</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.0484092980957461</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.182777093946296</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.3407671727458096</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.06027576620501852</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.1908684134130064</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.2675198146544366</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.04173601406468452</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1516830923005987</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.1182732557442661</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.06258771529569702</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.1232611419834048</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.1166229675682487</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.001568484147698277</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.04412518030836335</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.1375167543868193</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.04758213706030524</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1288264236504922</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.1319644592322021</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.08063655104506748</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.1687352125502564</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.1749318859378227</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.1799261069180624</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.20791904391777</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.2634682752989074</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.1025894585445022</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1606361060487229</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-0.1493212097301101</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>-0.03452737038032296</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.236110290034367</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>-0.009382900406513326</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.02522060355718684</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.06934863678063345</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.1261519206299392</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.1282340057329176</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.4936168437945803</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05551586701082299</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.2414396650489136</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2820421701998607</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.04299136433173667</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.2006903548373362</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1837746133703574</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1543522925079109</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.03492500492167466</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.02786372798752051</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.310354441997835</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.000837643414145372</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2235066648300265</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1253738319836764</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.1447044677449079</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.9173011440949848</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1994028427361483</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.211731703328831</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.03926249529111744</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.07522557291777775</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1586552214707025</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.04682506074512637</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.1198044286637819</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.135662098558752</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.4298662480690543</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.005725077753720755</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.2784648533327388</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.266883055565073</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.05558941272613765</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.199689961063344</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.238981839579549</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.09311063341602747</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.008301125095228947</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.2459947020432721</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.04681013619634984</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.2171280032683686</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.04867284988966423</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.145869899500718</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.05694023097771487</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.1052685328392949</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.01765487381758854</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.006884426439174628</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.04747929946279456</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.003614643010800851</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.1634957709217714</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.08393990120278941</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.1360910827810494</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.07042770003937636</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.153143608548903</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.1855991665865628</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.06910072750767995</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.2761412025221334</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.08837224519780114</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1843507096757481</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.2649951651063477</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.06456172435580759</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.2856776864030258</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0.02997379198639199</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.003412284039637023</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.1609556586251178</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.1022934243274434</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.1117438563314378</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.461844266741912</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01658413167368952</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2495191489291213</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3297609970446339</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.05293377328220761</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1873727862847769</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1488989462740125</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.1705492621610323</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.03623620256103131</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.0932094096693722</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.2960286272508294</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.1072582101360564</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1962897030284999</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1112320425494206</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1359316989870654</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.7440028745776951</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.2148628557129936</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.2410356340325725</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.0117113300985839</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.09434481136121495</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.2227310786262786</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.05026495778617871</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.117519990092683</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.05905377682496751</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.3629169633621047</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.05573855279647101</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.1721991121534836</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.2460185250107627</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.02822792693502324</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1647060054739684</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.2402472777386282</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.1193011285097275</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.04698829808150303</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.2265528284840596</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.04055241414672366</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1633354863026657</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.06032189990864194</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.06083085253739902</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.001236549384665623</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.07507582787394224</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.05477521371714018</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.1176806221062813</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.04604041724220517</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1183849603867285</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.09939808648504811</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.07585748336711942</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.06963726065123144</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.0660967299997864</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.1091556605138885</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.08249775917829315</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1446999248924977</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.2576371652163599</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.06287293522681392</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.133464749105798</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.3080922671229658</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.1167655375331608</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.273082031638717</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.04834540092342954</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.001828443302222537</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.1312288428301928</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.05242891010962882</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.03581262735916998</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5070594854974348</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.08504451812674586</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.02224761472387065</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.1157524701160362</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4818942710625743</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.160957767860414</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.09136565302084473</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.05397912216535049</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1268482426813632</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1314967751067522</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.1305911198235127</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.00872167993911944</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.01118102615856042</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.2700943956929857</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.2030708057305584</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.06217838429295218</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2307094641697861</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.08226527871472546</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.07145294485817721</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.163931719494037</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.6739145256189697</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.01022003198855631</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.2541303395583421</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1413156589997346</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.06498715308516392</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.1502139521952972</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.07532907131491942</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.05450087620234718</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.05506080801188731</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.01124328994107042</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.1425575212383878</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.00424562631913288</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.3249842644190324</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.05307955775709433</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.07498199128350254</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.1150066249217</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.2108229804750938</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.06270354222394092</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0341055441204622</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.04599245778463251</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1701578104011787</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1306341186457673</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.1391311914685751</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.07603943392483867</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.1828544827189851</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.06389140080564633</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.01857932071229898</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0483969747326672</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.02804932022016869</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.014820176576817</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.2898654840767083</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0.003798184836739563</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.1250326761161878</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.01604744395361469</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.06923615921434777</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.06652335917436705</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.1363287845154489</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.03624788932512778</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0.06626411359683071</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0.03861119954864092</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.06533814585403472</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.07963419625725961</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.001437313538485284</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.003991020833647495</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.06605540945448672</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0.02834297655004713</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.02338939921049627</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.1361844080545338</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.2261002149473959</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.05763961743540046</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.01738798850059292</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.03102422251916665</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.1023919026725243</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.1021648627682147</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.02984673341194449</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.1277321956035096</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1852054645855729</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.274164188982821</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.01047815702670177</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.1031203858278582</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.1401969196324653</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0.09450319710859478</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.02191006977092581</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.2583633417860902</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.0398668940929907</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2628937771389445</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1753761747644191</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.03476448466706715</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1839760092029472</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.1025351115599122</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.0006425454754551899</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.03162082657487063</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.02472954545518445</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1836806058591949</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.05396542589174899</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1056526340787783</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.09433892226975281</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.153033083568504</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.3079260961080305</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.08265440080399955</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1546677613915576</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.08099175539142765</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.1940318885617895</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.1344338679191212</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.01906670131300144</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.05239837870954855</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.04021735686952029</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.2050396724987587</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.007606150504098261</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.09606876053145703</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.1212016388140961</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.006994161010638468</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.09216944716290991</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1047929433125816</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1906354379407732</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.07020884613628176</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1164438465948621</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.002988421372379994</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.09059426788720255</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.002071646985762004</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.0734031446712332</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.008065089907953012</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.01255625205671837</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.03548588667522695</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.02403957970596777</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>7.075500156652039e-05</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.04768819354377264</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.003069441754497871</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.04732001981369759</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.02195592089293784</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>-0.02108485418202832</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.1094558877089583</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.08060430542290339</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.1119794121657161</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1333092310398285</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.002990910271766694</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.07343290514482848</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1555459584130055</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.04635993038536577</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.1041193082819837</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.1363108893833395</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.01223443452411322</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.07189106500424075</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.08175806910931974</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.009493103872618751</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4797667405914107</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.009133564751300335</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2177016651005572</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5852201125015042</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.1297723944971974</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1653457130048936</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1101597280191836</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.01636199894587489</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.08320802075104859</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.007141925829105581</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1064334383194103</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.03046788822858576</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1451666511937916</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.06334080485811022</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.08893779296734011</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.5996349008017985</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2609639490716745</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.2369318839039459</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.1665586041773112</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.004325984733476592</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.01190230471200147</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.01825145423621825</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.07393368009529079</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.03078643963866471</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.3624398595909631</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.02177775897574008</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.1214157553128597</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1962541453608726</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.02162816550569585</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.07295192589585875</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.09138331188091887</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.09664925269089084</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.04636506273882741</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1882433131732145</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.0203702264910936</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.08525963949229554</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.01009536960526744</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.01489646826073432</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.0692855319979956</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.06822885509277786</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.03591363780139042</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.09158519232172985</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.1314321999898786</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.05600578220350388</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.09427691784786556</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.1139903273968637</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.04005564808214564</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.01492391412253137</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.08426187941483591</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.002660719894234581</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.04914456529835368</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2137255844726937</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.0028963618112047</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.09053139576727857</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.09633551498023163</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.01216323090963714</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.07264014592881594</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.1659420297271451</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.04128623731934875</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.00709956036204493</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1104038917543697</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.0426152093146365</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.4961863920060907</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1567326105116253</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.06983692781384546</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.6254476511610683</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.304886567526668</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1805777993113766</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.06810487241496815</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01886613514049642</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.002103362544693323</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.0496823786823726</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1690699455237701</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2788737545677176</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1794898514702752</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.06071514713368366</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.2928077791654923</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.2755520802394067</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.185333128620785</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.0569411603017593</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.0394131988987451</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.004234282371556552</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.1422781488966285</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1496302649152298</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.1227683010464339</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.006039352181742033</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.2049752587182118</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.08021180039628857</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.01204226668740459</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.2408781289855911</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.07887914248316112</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.005303393747182267</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.1397918449536206</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0.1539690843285213</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.1079098011119705</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.2498429959067522</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.07972169849108475</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.02406371620262775</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1724599501309839</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.02686514339165121</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.0004801906620851312</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.1045867756875083</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0.06929821845153065</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.05255871900847025</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.03434069471522218</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.07037396103691673</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.02444503207342992</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.2839774353166377</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.05123467221408295</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.04151034220435001</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.1680528165161678</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0.04440263331868902</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.02189209900535474</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.278255659954341</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0.09725144446372005</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.006834945172132289</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1016155940066093</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.1221649195677776</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.09520427966786345</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.2181525051187369</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.004886462187274376</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.09054229985198031</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.2223244551364039</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0.00160589128942235</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3731230966163772</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.0420119052713564</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1519967645707042</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5114096768604545</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.1314644279615547</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.2298414526665896</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1059847255371112</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1239327724257471</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.003692964509654546</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.02481589348599168</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.2852387921779427</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.005883904099942509</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.03253196490208723</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.04508618354797846</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.02148416880675669</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.484734091313733</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2618613294231842</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.100872759032485</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.02740839907287607</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.0170139464554738</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.07636416204772974</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.06583359639185188</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.08109149286247117</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.0309351200133408</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.2604614951639241</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.08183622510665269</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.09134239028764626</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.107958548985595</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.03243570484548945</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.04958527758706763</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.1473096280980469</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1250850613702314</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.1024362216052699</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1091074693733954</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.01151657639985174</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.07038002457888469</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.04681290746384328</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1707249654454656</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.04162489024834271</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.011396451084524</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.05079057700530599</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.0683773996895669</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.01679069389854348</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.08180964000143437</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.0356200324368383</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.03651482864839592</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.02274182718972386</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.009250132885407386</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.009917387067506004</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.01136986722426154</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1187451900952809</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1288599505061859</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.002711634422247438</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.0391519035327915</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1979892506498809</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.1015970407047229</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1136250894637365</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.009635546239645432</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.02707643154592556</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.04485091585740351</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.03023292655681834</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.06345344347973311</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
